--- a/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,250 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 창고 경로 배정 시스템이 이제 그냥 컴퓨터가 아니거든요. 제 움직임을 다 기록하고 스캐너를 통해서 메시지를 보내요. 제가 고참이라서 저를 밀어내려고 하는 거예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 최근에 약물이나 술을 사용하신 적 있으세요? 아니면 과거에 정기적으로 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] '정기적으로'라는 게 정확히 무슨 뜻인지 잘 모르겠네요. 그런 걸 딱히 기록해 놓지도 않았고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 메시지들을 알아차리고 시스템이 자신을 표적으로 삼고 있다고 느끼신 지 얼마나 되셨어요? 며칠, 몇 주, 아니면 그보다 더 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 꽤 됐어요. 한 1년 8개월쯤 된 것 같아요. 그때쯤부터 스캐너가 메시지를 보내기 시작했고, 그게 계속 이어지고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이 기간 동안 유난히 활기차거나 들뜨고, 평소보다 잠을 훨씬 적게 자도 괜찮았던 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 그런 적은 없었던 것 같아요. 유난히 활기가 넘치거나 잠을 덜 자도 됐던 건 못 느꼈어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 한 달 동안 술이나 대마초, 각성제, 다른 약물을 사용하신 적이 있는지, 있다면 얼마나 자주, 얼마나 많이 사용하셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그걸 어떻게 답해야 할지 잘 모르겠네요. 뭘 얼마나 자주 썼는지 기록해 놓지 않아서요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 한 달 동안 단 한 번이라도 술이나 대마초, 다른 약물을 사용하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 지난 한 달 동안 뭔가를 썼는지 안 썼는지 딱히 기록해 놓지 않았거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 1년 8개월 동안 지속적으로 슬프거나 절망적이거나, 예전에 즐기시던 일들에 흥미를 잃었던 시기가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 네. 예전에 즐기던 것들이 이제 더 이상 끌리지 않아요. 낚시, 합창 연습, 차고에서 목공 작업하는 것—낚싯대나 연장을 그냥 바라만 봐도 손대고 싶은 마음이 전혀 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 낚시나 합창, 목공에 흥미가 없어지신 게, 스캐너 메시지가 시작된 시기랑 비교했을 때 얼마나 오래되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 꽤 오래됐어요. 낚시나 합창, 목공은 예전엔 저를 차분하게 해줬는데, 지금은 낚싯대나 연장 앞에 서 있어도 아무것도 하고 싶은 마음이 안 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 약 1년 8개월 전 스캐너 메시지가 시작된 이후로, 그 기간 동안 술이나 대마초, 다른 물질을 정기적으로 사용하셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 솔직히 확실하게 말씀드리기 어려워요. 그 기간 동안 뭔가를 정기적으로 썼는지 기록해 놓지 않았거든요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 이 1년 8개월 동안, 스캐너가 메시지를 보낸다고 느끼시면서도 슬프거나 흥미를 잃은 느낌은 없었던 시기가 있었나요? 즉, 그 정신증적 경험이 우울감 없이 나타난 적이 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 네. 한동안 기분이 좀 나아졌던 시기가 있었어요. 밥도 좀 더 먹고 말도 좀 더 했는데, 그런데도 몇 주 동안은 계속 배차 시스템이 제 번호를 부르는 소리가 들리고, 경로 배정 시스템이 저를 추적하고 있다는 느낌이 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 기분이 나아졌지만 여전히 배차 메시지가 들렸던 그 시기가, 대략 몇 주나 몇 달 정도 지속됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 몇 달까진 아니고 몇 주 정도였던 것 같아요. 그때는 기분이 좀 나았는데, 배차 메시지랑 추적당하는 느낌은 그대로 있었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 망상장애 (D004); 조현병 (D005) | 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>진단명: 조현정동장애 (우울형) (D007)
 인구통계: 성별 남성 / 나이 62 / 직업상태 industrial truck or tractor operator / 최종학력 전문학사
@@ -575,317 +810,45 @@
 증상 지속 기간: 2 years and 3 months
 추가 요건: psychotic_symptoms and depressive_episode occur concurrently, depressive_episode is present for the majority of the total duration of the active and residual portions of the illness (Criterion C), delusions_and_hallucinations occur for 2 or more weeks in the absence of a major mood episode (Criterion B)
 주호소 증상 코드: S019
-배경 서술: 조니가 일하던 창고에 자동 경로 배정 시스템이 도입되고 여러 고참 작업자들이 교대 야간 근무로 배치되면서, 수십 년간 그가 의지해 온 규칙적인 생활—아침 산책, 혈압 체크, 후배 지도, 그리고 차고에서 보내는 저녁 시간—이 흐트러지기 시작했다. 이후 2년 3개월에 걸쳐, 처음에는 새로운 스캐너와 교대 근무를 둘러싼 갈등에 대한 불만처럼 보이던 것이 점차 고정되고 반박하기 어려운 믿음과 생생한 지각 경험으로 굳어졌고, 동시에 우울 증상의 악화로 낚시, 복음성가 합창 모임, 목공, 가족 식사 시간에서 점점 멀어졌다. 그의 수면, 식욕, 움직임, 의욕, 자기 가치감은 직장에서 안전하게 일할 수 없을 정도로, 그리고 집에서 평소의 책임을 점점 더 수행할 수 없을 정도로 악화되었다. 지게차 주변에서 조리 없는 행동을 보인 심각한 창고 사고 이후, 산업보건팀과 아내, 그리고 주치의가 함께 긴급 정신건강의학과 평가를 조율하면서 정신과 진료가 시작되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생님입니다. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 창고 경로 배정 시스템이 이제 그냥 컴퓨터가 아니거든요. 제 움직임을 다 기록하고 스캐너를 통해서 메시지를 보내요. 제가 고참이라서 저를 밀어내려고 하는 거예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 최근에 약물이나 술을 사용하신 적 있으세요? 아니면 과거에 정기적으로 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] '정기적으로'라는 게 정확히 무슨 뜻인지 잘 모르겠네요. 그런 걸 딱히 기록해 놓지도 않았고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 메시지들을 알아차리고 시스템이 자신을 표적으로 삼고 있다고 느끼신 지 얼마나 되셨어요? 며칠, 몇 주, 아니면 그보다 더 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 꽤 됐어요. 한 1년 8개월쯤 된 것 같아요. 그때쯤부터 스캐너가 메시지를 보내기 시작했고, 그게 계속 이어지고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이 기간 동안 유난히 활기차거나 들뜨고, 평소보다 잠을 훨씬 적게 자도 괜찮았던 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 그런 적은 없었던 것 같아요. 유난히 활기가 넘치거나 잠을 덜 자도 됐던 건 못 느꼈어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 한 달 동안 술이나 대마초, 각성제, 다른 약물을 사용하신 적이 있는지, 있다면 얼마나 자주, 얼마나 많이 사용하셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그걸 어떻게 답해야 할지 잘 모르겠네요. 뭘 얼마나 자주 썼는지 기록해 놓지 않아서요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 한 달 동안 단 한 번이라도 술이나 대마초, 다른 약물을 사용하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 잘 모르겠어요. 지난 한 달 동안 뭔가를 썼는지 안 썼는지 딱히 기록해 놓지 않았거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 주요우울장애 (D015) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 1년 8개월 동안 지속적으로 슬프거나 절망적이거나, 예전에 즐기시던 일들에 흥미를 잃었던 시기가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 네. 예전에 즐기던 것들이 이제 더 이상 끌리지 않아요. 낚시, 합창 연습, 차고에서 목공 작업하는 것—낚싯대나 연장을 그냥 바라만 봐도 손대고 싶은 마음이 전혀 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 낚시나 합창, 목공에 흥미가 없어지신 게, 스캐너 메시지가 시작된 시기랑 비교했을 때 얼마나 오래되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 꽤 오래됐어요. 낚시나 합창, 목공은 예전엔 저를 차분하게 해줬는데, 지금은 낚싯대나 연장 앞에 서 있어도 아무것도 하고 싶은 마음이 안 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 약 1년 8개월 전 스캐너 메시지가 시작된 이후로, 그 기간 동안 술이나 대마초, 다른 물질을 정기적으로 사용하셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 솔직히 확실하게 말씀드리기 어려워요. 그 기간 동안 뭔가를 정기적으로 썼는지 기록해 놓지 않았거든요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 조현정동장애 (우울형) (D007); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 이 1년 8개월 동안, 스캐너가 메시지를 보낸다고 느끼시면서도 슬프거나 흥미를 잃은 느낌은 없었던 시기가 있었나요? 즉, 그 정신증적 경험이 우울감 없이 나타난 적이 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 네. 한동안 기분이 좀 나아졌던 시기가 있었어요. 밥도 좀 더 먹고 말도 좀 더 했는데, 그런데도 몇 주 동안은 계속 배차 시스템이 제 번호를 부르는 소리가 들리고, 경로 배정 시스템이 저를 추적하고 있다는 느낌이 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 기분이 나아졌지만 여전히 배차 메시지가 들렸던 그 시기가, 대략 몇 주나 몇 달 정도 지속됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 몇 달까진 아니고 몇 주 정도였던 것 같아요. 그때는 기분이 좀 나았는데, 배차 메시지랑 추적당하는 느낌은 그대로 있었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
+배경 서술: 조니가 일하던 창고에 자동 경로 배정 시스템이 도입되고 여러 고참 작업자들이 교대 야간 근무로 배치되면서, 수십 년간 그가 의지해 온 규칙적인 생활—아침 산책, 혈압 체크, 후배 지도, 그리고 차고에서 보내는 저녁 시간—이 흐트러지기 시작했다. 이후 2년 3개월에 걸쳐, 처음에는 새로운 스캐너와 교대 근무를 둘러싼 갈등에 대한 불만처럼 보이던 것이 점차 고정되고 반박하기 어려운 믿음과 생생한 지각 경험으로 굳어졌고, 동시에 우울 증상의 악화로 낚시, 복음성가 합창 모임, 목공, 가족 식사 시간에서 점점 멀어졌다. 그의 수면, 식욕, 움직임, 의욕, 자기 가치감은 직장에서 안전하게 일할 수 없을 정도로, 그리고 집에서 평소의 책임을 점점 더 수행할 수 없을 정도로 악화되었다. 지게차 주변에서 조리 없는 행동을 보인 심각한 창고 사고 이후, 산업보건팀과 아내, 그리고 주치의가 함께 긴급 정신건강의학과 평가를 조율하면서 정신과 진료가 시작되었다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - S020 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+  - S022 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.
+  - S023 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).</t>
+        </is>
+      </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>[11번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004); 조현병 (D005) | 중간확률: 외상후 스트레스장애 (D018) | 배제됨: 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 제1형 양극성장애 (D008); 제2형 양극성장애 (D009); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 조현정동장애 (우울형) (D007, ICD: F25.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.6667</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: 와해된 사고/언어: 논리적이고 일관된 흐름이 부족해 말이나 생각이 흩어지고 따라가기 어려운 증상.; 와해된/비정상적 행동: 행동과 운동 조절이 심각하게 손상되어 상황에 맞지 않는 움직임이나 반응으로 나타나는 상태.; 음성 증상: 정상적으로 존재해야 할 감정, 동기, 언어, 사회적 관심이 감소하거나 상실된 상태.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
-  확인된 근거: 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
-  누락: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.; 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 조현정동장애 (우울형) (D007, ICD: F25.1)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: 0.6667
+체크리스트 그룹: psychotic_symptoms (관계=must_include, 요구개수=2, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=1, 커버리지=0.2)
+확인된 근거:
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+체크리스트 그룹: delusions_and_hallucinations (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
+  - 환각: 외부 자극 없이 발생하지만 정상적인 지각만큼 생생하고 뚜렷한 지각 경험.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
@@ -796,6 +796,11 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -844,11 +849,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A49:B49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D007_S004_P001__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.3515</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.8636</v>
+        <v>0.7121</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3561</v>
+        <v>0.4849</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.8333</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
